--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.441957081239008</v>
+        <v>1.209318025701339</v>
       </c>
       <c r="D2" t="n">
-        <v>7.683957025817017</v>
+        <v>1.248643016695265</v>
       </c>
       <c r="E2" t="n">
-        <v>25.78327170753688</v>
+        <v>4.189781652474744</v>
       </c>
       <c r="F2" t="n">
-        <v>26.04380233670571</v>
+        <v>4.232117879714678</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.00850049631277</v>
+        <v>9.588881330650825</v>
       </c>
       <c r="D3" t="n">
-        <v>59.77156169922843</v>
+        <v>9.71287877612462</v>
       </c>
       <c r="E3" t="n">
-        <v>25.78327170753688</v>
+        <v>4.189781652474744</v>
       </c>
       <c r="F3" t="n">
-        <v>26.04380233670571</v>
+        <v>4.232117879714678</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
